--- a/第三類_AI代理與指南企劃/interview_analyzer/data/職缺需求與部門清單.xlsx
+++ b/第三類_AI代理與指南企劃/interview_analyzer/data/職缺需求與部門清單.xlsx
@@ -7,8 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="職缺需求與規格清單" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DISC 人格類型參考說明" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="彰濱廠區職缺清單" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="勝一總公司(高雄)職缺清單" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI建議參考職缺與規格擬定" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DISC 人格類型參考說明" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -37,7 +39,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -54,6 +56,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="002F5597"/>
         <bgColor rgb="002F5597"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0070AD47"/>
+        <bgColor rgb="0070AD47"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00333333"/>
+        <bgColor rgb="00333333"/>
       </patternFill>
     </fill>
   </fills>
@@ -83,7 +97,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -95,6 +109,12 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -462,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -508,12 +528,1093 @@
     <row r="2" ht="65" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>🛡️ 廠務與安衛類</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>警衛人員</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>1. 出入廠區登記、管控
+2. 來賓身分確認
+3. 承攬商身分確認
+4. 緊急狀況聯繫通知回報
+5. 主管交辦事項</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>工作經歷：經歷不拘
+學歷要求：高中
+待遇：月薪 34,000 元</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>S型 (S型80%+C型20%)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="65" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>🏭 化工生產類</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>化工助理工程師</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>1. 生產製程操作
+2. 所屬設備之操作保養與維護
+3. 責任區域負責、回報
+4. 其它主管交辦事項
+5. 需輪班 (刊登薪資已含輪班津貼及夜點費)</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>工作經歷：經歷不拘
+學歷要求：大學
+待遇：月薪 45,000~50,000 元</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>SC型 (S型60%+C型40%)</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="65" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>🔬 技術與建廠工程類</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>技術工程師</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>1. 協助建廠專案管理
+2. 生產管理
+3. 製程改善與最佳化
+4. 品質提升
+5. 異常分析、排除、預防
+6. SOP制定</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>工作經歷：1年以上
+學歷要求：碩士
+待遇：待遇面議</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>CD型 (C型70%+D型30%)</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="65" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>🏭 廠區管理與生產類</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>助理工程師</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>1. 槽車灌裝進出貨作業與過磅
+2. 包材灌裝作業
+3. 產品調和作業
+4. 堆高機操作作業
+5. 設備保養檢查作業
+6. 作業環境6S檢查與維護</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>工作經歷：經歷不拘
+學歷要求：專科
+待遇：月薪 41,000~45,000 元</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>CS型 (C型60%+S型40%)</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="65" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>🔬 品管檢驗類</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>品管助理工程師</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>1. 現場分析工作
+2. 儀器校正
+3. 取樣及送樣作業
+4. 執行主管分配任務 (夜點費另計)</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>工作經歷：1年以上
+學歷要求：大學
+待遇：月薪 41,000~45,000 元</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>C型 (C型80%+S型20%)</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="65" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>🔬 品質保證類</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>品保工程師</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>1. 進料、製程、成品品質監控
+2. 品質異常之原因分析及後續處理
+3. 品保改善工程師 / 品質系統稽核 / 客戶服務</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>工作經歷：1年以上
+學歷要求：碩士
+待遇：待遇面議</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>C型 (C型80%+D型20%)</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="65" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>💼 業務行政類</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>業務助理管理師</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>1. T100系統進出貨相關作業
+2. 月底結帳、發票作業
+3. 業務及主管交辦事項處理</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>工作經歷：經歷不拘
+學歷要求：專科
+待遇：月薪 37,000~40,000 元</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>SC型 (S型60%+C型40%)</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="65" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>⚡ 工程與儀電類</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>儀電(儀表)工程師</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>1. 廠內設備維護保養
+2. 製程設備突發狀況處理
+3. 建廠及專案工程執行
+4. 主管交辦事項處理</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>工作經歷：經歷不拘
+學歷要求：大學
+待遇：待遇面議</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>CS型 (C型70%+S型30%)</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="65" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>🔬 製程工程類</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>製程工程師</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>1. 建立製程產品系統完整化
+2. 生產品質追蹤與維持
+3. 專案工程執行與追蹤
+4. 異常處理與改善</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>工作經歷：3年以上
+學歷要求：碩士
+待遇：待遇面議</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>CD型 (C型70%+D型30%)</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>部門類別</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>職缺名稱</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>104工作內容 (Job Description)</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>條件要求 (Requirements)</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>推薦黃金 DISC 型態</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>快捷標籤</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="65" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>💼 總部行政與財務類</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>會計行政人員 / 財務專員</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>1. 應收/應付款項帳務處理與傳票開立
+2. 零用金管理與費用報銷審核
+3. 月結報表編製與營業稅申報協助</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>工作經歷：1~2年以上會計經驗
+學歷要求：專科、大學</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>C型 (C型80%+S型20%)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="65" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>💼 總部人資與管理類</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>人資 (HR) 招募/訓練管理師</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>1. 104職缺維護、履歷篩選與面談邀約
+2. 員工教育訓練課程規劃與執行
+3. 考勤管理與薪酬核算</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>工作經歷：2年以上 HR 經驗
+學歷要求：大學以上</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>IS型 (I型60%+S型40%)</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="65" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>🔬 研發品保類</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>研發 (RD) 化學工程師</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>1. 特用化學品與電子級溶劑配方研發
+2. 實驗室分析儀器操作 (GC, HPLC, ICP-MS)
+3. 研發專利檢索與技術報告撰寫</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>工作經歷：1~3年化學研發經驗
+學歷要求：碩士、大學</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>C型 (C型80%+D型20%)</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="65" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>📦 採購資材類</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>採購專員</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>1. 化工原物料、廠務設備及耗材詢價比價與採購
+2. 供應商評鑑、考核與日常關係維護
+3. 採購合約擬定與交期追蹤管控</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>經歷：2年以上製造業採購經驗
+學歷：大學以上 (化學、化工、商管相關)
+待遇：月薪 38,000~50,000 元</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>CD型 (C型60%+D型40%)</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="65" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>🔬 品質保證類</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>品保工程師 (高雄)</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>1. 進料、半成品及成品之化學分析與質檢監測
+2. 分析儀器 (GC, HPLC, ICP-MS) 操作與校正
+3. ISO 9001/IATF 16949 品質管理系統維護</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>經歷：1年以上化學品檢驗分析經驗
+學歷：大學以上
+待遇：月薪 36,000~48,000 元</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>C型 (C型90%+S型10%)</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="65" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>⚡ 廠務設備工程類</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>廠務(機械/電機)工程師</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>1. 高雄總廠與路竹廠建廠/擴廠工程規劃與監督
+2. 化工管道、槽區與旋轉機械設備定期檢驗保養
+3. PLC 程式邏輯控制與電氣控制迴路維護</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>經歷：2年以上廠務工程或化工設備經驗
+學歷：專科、大學 (機械、電機相關)</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>CS型 (C型70%+S型30%)</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="65" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>📦 物料倉儲管理類</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>高級倉管員 / 物料控制師</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>1. 原料、半成品及危險化學品庫位規劃與盤點
+2. 槽車進出貨過磅及堆高機裝卸作業
+3. ERP 系統物料帳務精準登錄與料號核對</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>經歷：1~3年危險物料倉庫管理經驗
+學歷：高中職以上
+證照：堆高機操作合格證照</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>SC型 (S型70%+C型30%)</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="65" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>🛡️ 職業安全衛生類</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>環安衛管理師 (高雄)</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>1. 全廠 ISO 14001 / ISO 45001 管理體系維護
+2. 化學品危害通識、緊急應變演練與工安稽核
+3. 環保許可證申請、廢水廢氣申報作業</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>經歷：2年以上安衛管理經驗
+學歷：專科、大學 (環安衛相關)
+證照：乙級職業安全衛生管理員</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>CS型 (C型70%+S型30%)</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="65" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>💻 資訊與數位轉型類</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>資訊系統 (ERP/T100) 工程師</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>1. 鼎新 T100 ERP 系統維護、4GL 程式開發與報表產出
+2. 跨部門作業流程優化與資料庫 (Oracle/SQL) 維護
+3. 企業資訊安全管理與伺服器網路設備維護</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>經歷：2年以上 ERP 開發或維護經驗
+學歷：大學 (資訊工程、資管相關)</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>CD型 (C型80%+D型20%)</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="65" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>💼 國內外業務類</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>國外業務專員 / 經理</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>1. 特用化學品與電子級溶劑海外市場開發與客戶維繫
+2. 參加國際展會、商務談判與合約簽訂
+3. 訂單追蹤、出貨報關與應收帳款管理</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>經歷：2~5年化學品或半導體材料外銷經驗
+學歷：大學以上 (語言、商管、化工相關)
+語言：英文精通 (TOEIC 800+)</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>DI型 (D型50%+I型50%)</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="65" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>🔬 技術服務與應用類</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>技術服務 (TS) 化學工程師</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>1. 協助半導體及面板客戶進行產品測試與應用開發
+2. 客訴品質異常原因分析與到廠技術支援
+3. 撰寫產品技術規格書 (TDS) 與安全資料表 (SDS)</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>經歷：1~3年半導體或化學品技術服務經驗
+學歷：碩士、大學 (化工、化學相關)</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>IC型 (I型50%+C型50%)</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="65" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>📦 資材物料類</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>生管 (生產排程) 專員</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>1. 生產計劃 (MPS) 與物料需求計劃 (MRP) 編製
+2. 產能平衡規劃、工單開立與生產進度追蹤
+3. 銷售訂單交期協調與產銷會議主持</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>經歷：2年以上製造業生管經驗
+學歷：專科、大學 (工管、資材相關)</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>CS型 (C型70%+S型30%)</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="65" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>🛡️ 綠能與ESG發展類</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>永續發展 (ESG) / 碳盤查專員</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>1. 溫室氣體盤查 (ISO 14064-1) 與產品碳足跡計算
+2. ESG 永續報告書編撰與第三方查證對接
+3. 減碳專案規劃、節能減碳目標追蹤與評估</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>經歷：1年以上 ESG 或環境管理經驗
+學歷：大學以上</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>CS型 (C型60%+S型40%)</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="65" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>🔬 實驗室檢驗類</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>分析化學實驗室檢驗員</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>1. 原料、半成品及水質化驗與樣品檢測
+2. 檢驗數據紀錄、輸入與異常回報
+3. 實驗室藥品、玻璃儀器與化學試劑管理</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>經歷：經歷不拘
+學歷：專科、大學 (化學、化工相關)</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>C型 (C型85%+S型15%)</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="65" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>🏭 生產製造類</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>化工製程現場技術員</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>1. 化學品反應器與蒸餾塔操作與監控
+2. 現場抄表、投料與取樣作業
+3. 輪班作業 (四二輪班 / 需配合夜班)</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>經歷：經歷不拘
+學歷：高中職、專科以上
+待遇：月薪 35,000~45,000 元 (輪班津貼另計)</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>SC型 (S型70%+C型30%)</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="65" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>⚡ 設備保修類</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>機械保修員</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>1. 幫浦、閥類、管路與轉動設備檢修拆裝
+2. 預防保養計劃執行與故障緊急搶修
+3. 保修零件庫存管理與安全作業維護</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>經歷：1年以上機械維修經驗
+學歷：高中職、專科 (機械、機電相關)</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>CS型 (C型60%+S型40%)</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="65" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>💼 總部法務類</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>法務專員 / 副理</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>1. 中英文商業合約審閱、撰擬與談判
+2. 公司智慧財產權 (專利/商標) 管理與維護
+3. 法律風險評估、法令遵循與訴訟對接</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>經歷：3年以上企業法務或律師事務所經驗
+學歷：大學以上 (法律相關科系)</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>CD型 (C型70%+D型30%)</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="65" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>💼 總部稽核類</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>內部稽核專員</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>1. 依據公開發行公司內部控制制度執行例行性與專案稽核
+2. 撰寫稽核報告與追蹤內控缺失改善進度
+3. 董事會與審計委員會會議資料準備</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>經歷：2年以上公開發行公司稽核或事務所經歷
+學歷：大學以上 (會計、財經、商管相關)</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>C型 (C型85%+D型15%)</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>部門類別</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>職缺名稱</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>104工作內容 (Job Description)</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>條件要求 (Requirements)</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>推薦黃金 DISC 型態</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>快捷標籤</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="65" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
           <t>🏭 勝一化工 &amp; 廠區管理類</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>【彰濱廠區】助理管理師</t>
+          <t>【彰濱廠區】助理管理師 (AI規劃範本)</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -553,7 +1654,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>資材部 - 現場助理工程師</t>
+          <t>資材部 - 現場助理工程師 (AI規劃範本)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -592,7 +1693,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>資材部 - 資材工程師</t>
+          <t>資材部 - 資材工程師 (AI規劃範本)</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -630,7 +1731,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>資材部 - 資材行政專員</t>
+          <t>資材部 - 資材行政專員 (AI規劃範本)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -667,7 +1768,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>會計行政人員 / 財務專員</t>
+          <t>會計行政人員 / 財務專員 (AI規劃範本)</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -693,7 +1794,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -705,7 +1806,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>倉管 / 物料管理員</t>
+          <t>倉管 / 物料管理員 (AI規劃範本)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -729,7 +1830,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -741,7 +1842,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>研發 (RD) 化學工程師</t>
+          <t>研發 (RD) 化學工程師 (AI規劃範本)</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -765,7 +1866,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -777,7 +1878,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>人資 (HR) 招募/訓練管理師</t>
+          <t>人資 (HR) 招募/訓練管理師 (AI規劃範本)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -801,7 +1902,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -810,7 +1911,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -826,22 +1927,22 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>DISC 類型代號</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>人格特徵名稱</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>核心特質與行為風格</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>建議適合之職務類型</t>
         </is>
